--- a/exports/WAAREEENER_full_report.xlsx
+++ b/exports/WAAREEENER_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q27"/>
+  <dimension ref="A1:U27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>20.9</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45604.55208333334</v>
+        <v>45607.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>3108.95</v>
+        <v>2883</v>
       </c>
       <c r="I2" t="n">
         <v>2991.1692658</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K2" t="n">
-        <v>3.91</v>
+        <v>-3.64</v>
       </c>
       <c r="L2" t="n">
         <v>4.23</v>
@@ -555,7 +578,7 @@
         <v>1.62</v>
       </c>
       <c r="N2" t="n">
-        <v>7.82</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="O2" t="n">
         <v>3.41</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>26.2</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>45632.55208333334</v>
+        <v>45635.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>2893</v>
+        <v>2915</v>
       </c>
       <c r="I3" t="n">
         <v>2906.072295197217</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.35</v>
+        <v>-1.11</v>
       </c>
       <c r="L3" t="n">
         <v>10.51</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>8.380000000000001</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>45645.55208333334</v>
+        <v>45646.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>3041.3</v>
+        <v>2938.8</v>
       </c>
       <c r="I4" t="n">
         <v>2991.335969567438</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>4.33</v>
+        <v>0.82</v>
       </c>
       <c r="L4" t="n">
         <v>0.45</v>
@@ -669,7 +716,7 @@
         <v>3.09</v>
       </c>
       <c r="N4" t="n">
-        <v>2.83</v>
+        <v>5.57</v>
       </c>
       <c r="O4" t="n">
         <v>2.73</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>13.05</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>45707.55208333334</v>
+        <v>45708.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>2216.9</v>
+        <v>2329</v>
       </c>
       <c r="I5" t="n">
         <v>2312.313854466851</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K5" t="n">
-        <v>24.56</v>
+        <v>20.75</v>
       </c>
       <c r="L5" t="n">
         <v>5.01</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>11.47</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45748.55208333334</v>
+        <v>45750.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>2380.75</v>
+        <v>2214.75</v>
       </c>
       <c r="I6" t="n">
         <v>2264.860501556948</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>42</v>
       </c>
       <c r="K6" t="n">
-        <v>2.22</v>
+        <v>-4.91</v>
       </c>
       <c r="L6" t="n">
         <v>11.28</v>
       </c>
       <c r="M6" t="n">
-        <v>1.74</v>
+        <v>5.92</v>
       </c>
       <c r="N6" t="n">
-        <v>4.35</v>
+        <v>6.33</v>
       </c>
       <c r="O6" t="n">
         <v>3.93</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9.83</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45762.55208333334</v>
+        <v>45763.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>2214.4</v>
+        <v>2223.5</v>
       </c>
       <c r="I7" t="n">
         <v>2221.113072877105</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02</v>
+        <v>-0.4</v>
       </c>
       <c r="L7" t="n">
         <v>2.24</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45772.38541666666</v>
+        <v>45772.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>2699.4</v>
+        <v>2668.1</v>
       </c>
       <c r="I8" t="n">
         <v>2682.57047825674</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K8" t="n">
-        <v>21.4</v>
+        <v>20</v>
       </c>
       <c r="L8" t="n">
         <v>1.03</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>15.12</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45792.38541666666</v>
+        <v>45792.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>2800.9</v>
+        <v>2895</v>
       </c>
       <c r="I9" t="n">
         <v>2842.375477132867</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.98</v>
+        <v>-8.5</v>
       </c>
       <c r="L9" t="n">
-        <v>7.61</v>
+        <v>8.69</v>
       </c>
       <c r="M9" t="n">
         <v>3.69</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45825.55208333334</v>
+        <v>45826.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>2786</v>
+        <v>2714.9</v>
       </c>
       <c r="I10" t="n">
         <v>2754.438042493209</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>33</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K10" t="n">
-        <v>-3.77</v>
+        <v>-6.22</v>
       </c>
       <c r="L10" t="n">
         <v>7.98</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>8.42</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45827.55208333334</v>
+        <v>45828.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>2670</v>
+        <v>2887.7</v>
       </c>
       <c r="I11" t="n">
         <v>2858.639265333206</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>1.65</v>
+        <v>-6.36</v>
       </c>
       <c r="L11" t="n">
-        <v>2.46</v>
+        <v>6.77</v>
       </c>
       <c r="M11" t="n">
         <v>0.33</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>12.66</v>
       </c>
       <c r="O11" t="n">
         <v>-3.34</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>12.05</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45868.55208333334</v>
+        <v>45869.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>3157.2</v>
+        <v>3006.1</v>
       </c>
       <c r="I12" t="n">
         <v>3066.831874043032</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K12" t="n">
-        <v>9.33</v>
+        <v>4.1</v>
       </c>
       <c r="L12" t="n">
         <v>7.37</v>
       </c>
       <c r="M12" t="n">
-        <v>1.53</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>3.19</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
         <v>12.66</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>9.92</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45889.38541666666</v>
+        <v>45889.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>3095</v>
+        <v>3142</v>
       </c>
       <c r="I13" t="n">
         <v>3131.912447510647</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.96</v>
+        <v>-4.52</v>
       </c>
       <c r="L13" t="n">
         <v>8.02</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.77</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>3447</v>
+        <v>3188.8</v>
       </c>
       <c r="I14" t="n">
         <v>3415.161406001028</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>36</v>
+        <v>36.83333333333334</v>
       </c>
       <c r="K14" t="n">
-        <v>9.710000000000001</v>
+        <v>1.49</v>
       </c>
       <c r="L14" t="n">
         <v>1.88</v>
@@ -1239,7 +1406,7 @@
         <v>3.96</v>
       </c>
       <c r="N14" t="n">
-        <v>5.66</v>
+        <v>7.17</v>
       </c>
       <c r="O14" t="n">
         <v>3.42</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,25 +1454,25 @@
         <v>11.82</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45943.55208333334</v>
+        <v>45944.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>3422.1</v>
+        <v>3506.2</v>
       </c>
       <c r="I15" t="n">
         <v>3470.110790138097</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K15" t="n">
-        <v>-7.32</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>8.789999999999999</v>
+        <v>12.04</v>
       </c>
       <c r="M15" t="n">
-        <v>1.26</v>
+        <v>1.56</v>
       </c>
       <c r="N15" t="n">
         <v>3.34</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>6.09</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45964.55208333334</v>
+        <v>45965.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>3422</v>
+        <v>3379</v>
       </c>
       <c r="I16" t="n">
         <v>3379.344947341713</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.4</v>
+        <v>-3.63</v>
       </c>
       <c r="L16" t="n">
-        <v>2.68</v>
+        <v>3.71</v>
       </c>
       <c r="M16" t="n">
         <v>0.04</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.51</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46010.38541666666</v>
+        <v>46010.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>2952.4</v>
+        <v>3057</v>
       </c>
       <c r="I17" t="n">
         <v>3010.872673948317</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>45</v>
+        <v>45.16666666666666</v>
       </c>
       <c r="K17" t="n">
-        <v>12.63</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="L17" t="n">
         <v>1.48</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>7.46</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46023.55208333334</v>
+        <v>46024.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>2955</v>
+        <v>2851.4</v>
       </c>
       <c r="I18" t="n">
         <v>2921.112744390228</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.34</v>
+        <v>-6.73</v>
       </c>
       <c r="L18" t="n">
-        <v>4.28</v>
+        <v>6.84</v>
       </c>
       <c r="M18" t="n">
         <v>0.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.23</v>
+        <v>2.98</v>
       </c>
       <c r="O18" t="n">
         <v>6.11</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>7.76</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46044.38541666666</v>
+        <v>46044.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>2600.9</v>
+        <v>2652.8</v>
       </c>
       <c r="I19" t="n">
         <v>2621.572290161531</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>8.789999999999999</v>
+        <v>6.96</v>
       </c>
       <c r="L19" t="n">
         <v>3.98</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>11.23</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46070.55208333334</v>
+        <v>46071.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>3044.8</v>
+        <v>2927.8</v>
       </c>
       <c r="I20" t="n">
         <v>2952.356587043412</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>14.78</v>
+        <v>10.37</v>
       </c>
       <c r="L20" t="n">
         <v>4.19</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>8.9</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46097.55208333334</v>
+        <v>46098.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>2782.9</v>
+        <v>2889</v>
       </c>
       <c r="I21" t="n">
         <v>2796.761412440187</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K21" t="n">
-        <v>4.95</v>
+        <v>1.33</v>
       </c>
       <c r="L21" t="n">
         <v>4.26</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46135.55208333334</v>
+        <v>46136.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>3399</v>
+        <v>3298.2</v>
       </c>
       <c r="I22" t="n">
         <v>3313.699514867546</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K22" t="n">
-        <v>17.65</v>
+        <v>14.16</v>
       </c>
       <c r="L22" t="n">
         <v>3.56</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>7.2</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46169.38541666666</v>
+        <v>46169.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>3048.9</v>
+        <v>3142</v>
       </c>
       <c r="I23" t="n">
         <v>3135.619590801107</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K23" t="n">
-        <v>7.56</v>
+        <v>4.74</v>
       </c>
       <c r="L23" t="n">
         <v>7.2</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>7.28</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46198.55208333334</v>
+        <v>46202.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>3010.6</v>
+        <v>2856</v>
       </c>
       <c r="I24" t="n">
         <v>2978.247098909376</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>29</v>
+        <v>32.83333333333334</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.18</v>
+        <v>-9.1</v>
       </c>
       <c r="L24" t="n">
-        <v>5.72</v>
+        <v>9.68</v>
       </c>
       <c r="M24" t="n">
         <v>1.96</v>
       </c>
       <c r="N24" t="n">
-        <v>2.06</v>
+        <v>4.17</v>
       </c>
       <c r="O24" t="n">
         <v>1.75</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>8.710000000000001</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46308.38541666666</v>
+        <v>46308.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>2423.7</v>
+        <v>2451</v>
       </c>
       <c r="I25" t="n">
         <v>2440.630312405282</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>106</v>
+        <v>106.1666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>15.14</v>
+        <v>14.18</v>
       </c>
       <c r="L25" t="n">
         <v>5.74</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>149</v>
+        <v>150</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>5.87</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46316.55208333334</v>
+        <v>46317.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>2434</v>
+        <v>2369.2</v>
       </c>
       <c r="I26" t="n">
         <v>2393.200270026722</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-3.34</v>
       </c>
       <c r="L26" t="n">
-        <v>1.83</v>
+        <v>3.65</v>
       </c>
       <c r="M26" t="n">
         <v>0.47</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1983,6 +2306,12 @@
       <c r="Q27" t="n">
         <v>8</v>
       </c>
+      <c r="R27" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2963,7 +3292,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>27.7</v>
+        <v>28.7</v>
       </c>
     </row>
     <row r="6">
@@ -2973,7 +3302,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.2</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="7">
@@ -2983,7 +3312,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>106</v>
+        <v>106.2</v>
       </c>
     </row>
     <row r="8">
@@ -2993,7 +3322,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -3003,7 +3332,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="10">
@@ -3013,7 +3342,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>43.1</v>
+        <v>43.9</v>
       </c>
     </row>
     <row r="11">
@@ -3023,7 +3352,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -3033,7 +3362,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -3043,7 +3372,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3053,7 +3382,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.15</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="15">
@@ -3063,7 +3392,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.3</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="16">
@@ -3073,7 +3402,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4.97</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="17">
@@ -3083,7 +3412,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.56</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="18">
@@ -3093,7 +3422,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
@@ -3103,7 +3432,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.95</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="20">
@@ -3113,7 +3442,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.26</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="21">
@@ -3123,7 +3452,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11.28</v>
+        <v>12.04</v>
       </c>
     </row>
     <row r="22">
@@ -3133,7 +3462,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -3143,7 +3472,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -3153,7 +3482,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.61</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="25">
@@ -3173,7 +3502,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.58</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="27">
@@ -3183,7 +3512,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.99</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="28">
@@ -3193,7 +3522,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
